--- a/阵营/帮会领地战.xlsx
+++ b/阵营/帮会领地战.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JX3\Game\JX3\bin\zhcn_hd\interface\MY#DATA\!all-users@zhcn_hd\userdata\team_mon\remote\打包\阵营\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{84E78CFD-66C6-45A3-A247-E3855BB46A32}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{A5752654-29BC-421B-A6BC-C519081B3CF5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1260" yWindow="1800" windowWidth="25110" windowHeight="12510" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2255" uniqueCount="1674">
+<sst xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" count="2270" uniqueCount="1675">
   <si>
     <t>标识</t>
   </si>
@@ -5254,10 +5254,6 @@
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
   <si>
-    <t>{nClass=14,nIcon=0,nFrame=4,szName="帮会宣战·领地·正式开启",nTime=5,key="帮会宣战",},</t>
-    <phoneticPr fontId="18" type="noConversion"/>
-  </si>
-  <si>
     <t>帮会宣战·领地·10秒</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
@@ -5386,6 +5382,14 @@
   </si>
   <si>
     <t>马嵬驿</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·正式开启",nTime=5,key="帮会宣战",},</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>门派的地图</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -6637,7 +6641,7 @@
     <row r="4" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A4" s="21" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1766075767270,</v>
+        <v>nTimeStamp = 1771136010880,</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>36</v>
@@ -12516,7 +12520,7 @@
         <v>153</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="M156" s="3" t="s">
         <v>1331</v>
@@ -17542,7 +17546,7 @@
         <v>{dwID=122226,nFrame=47,szNote="帮会大旗",col={255,255,255,},[3]={bScreenHead=true,},[4]={},aFocus={{dwMapID=-1,szDisplay="帮会大旗·800分",nMaxDistance=0,tRelation={bAll=true,bEnemy=false,bAlly=false,},tLife={bEnable=false,szOperator="&gt;",nValue=0,},},},tCountdown={{nClass=12,nIcon=591,nFrame=1,szName="帮会大旗·损毁·800分",nTime=30,key="帮会大旗·退场",},},},</v>
       </c>
       <c r="X19" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="20" spans="3:24" x14ac:dyDescent="0.15">
@@ -17690,7 +17694,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://purl.oclc.org/ooxml/spreadsheetml/main" xmlns:r="http://purl.oclc.org/ooxml/officeDocument/relationships" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A6EF65B-A46B-4484-9B98-C06436DB2528}">
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:S34"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="36" customWidth="1"/>
@@ -17717,7 +17721,7 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="G1" t="s">
         <v>1622</v>
@@ -17773,14 +17777,14 @@
         <v>1610</v>
       </c>
       <c r="E3" t="s">
+        <v>1643</v>
+      </c>
+      <c r="Q3" t="str">
+        <f t="shared" ref="Q3:Q34" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(I3),ISBLANK(J3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(I2)=FALSE,ISBLANK(J2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(H3&lt;&gt;"","col={"&amp;H3&amp;"},","")&amp;IF(I3&gt;0,"bSearch=true,","")&amp;IF(J3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(K3&gt;0,"szVoice="""&amp;K3&amp;""",","")&amp;IF(L3&gt;0,"bTeamChannel=true,","")&amp;IF(M3&gt;0,"bWhisperChannel=true,","")&amp;IF(N3&gt;0,"bCenterAlarm=true,","")&amp;IF(O3&gt;0,"bScreenHead=true,","")&amp;IF(P3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(R3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,R3:AAC3)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="最近七天内，帮会宣战·领地失利，已为侠士添加不利状态。",szNote="帮会宣战·领地·失败",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=8,szName="帮会宣战·领地·失败",nTime=30,key="帮会宣战",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
+      </c>
+      <c r="R3" t="s">
         <v>1644</v>
-      </c>
-      <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q29" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(I3),ISBLANK(J3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(I2)=FALSE,ISBLANK(J2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(H3&lt;&gt;"","col={"&amp;H3&amp;"},","")&amp;IF(I3&gt;0,"bSearch=true,","")&amp;IF(J3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(K3&gt;0,"szVoice="""&amp;K3&amp;""",","")&amp;IF(L3&gt;0,"bTeamChannel=true,","")&amp;IF(M3&gt;0,"bWhisperChannel=true,","")&amp;IF(N3&gt;0,"bCenterAlarm=true,","")&amp;IF(O3&gt;0,"bScreenHead=true,","")&amp;IF(P3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(R3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,R3:AAC3)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="最近七天内，帮会宣战·领地失利，已为侠士添加不利状态。",szNote="帮会宣战·领地·失败",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=8,szName="帮会宣战·领地·失败",nTime=30,key="帮会宣战",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
-      </c>
-      <c r="R3" t="s">
-        <v>1645</v>
       </c>
       <c r="S3" s="37" t="s">
         <v>1633</v>
@@ -17791,7 +17795,7 @@
         <v>1611</v>
       </c>
       <c r="E4" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="N4">
         <v>1</v>
@@ -17801,7 +17805,7 @@
         <v>{szContent="恭喜侠士帮会宣战·领地获胜！已为您添加增益状态。",szNote="帮会宣战·领地·获胜",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=0,szName="帮会宣战·领地·获胜",nTime=30,key="帮会宣战",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="R4" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="S4" s="37" t="s">
         <v>1633</v>
@@ -17812,10 +17816,10 @@
         <v>1612</v>
       </c>
       <c r="D5" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E5" t="s">
         <v>1667</v>
-      </c>
-      <c r="E5" t="s">
-        <v>1668</v>
       </c>
       <c r="H5" t="s">
         <v>1428</v>
@@ -17834,7 +17838,7 @@
         <v>{szContent="[帮会宣战][帮会大旗]已被敌方攻破！诸位兄弟！团结一致！",szTarget="%",szNote="帮会大旗·退场·800分",col={255,255,255,},[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=591,nFrame=1,szName="帮会大旗·损毁·800分",nTime=30,key="帮会大旗·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R5" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.15">
@@ -17882,7 +17886,7 @@
         <v>甄琦·退场·屋门前东侧·100分</v>
       </c>
       <c r="F7" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="G7" t="s">
         <v>1624</v>
@@ -17913,7 +17917,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.15">
       <c r="C8" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="D8" t="s">
         <v>1613</v>
@@ -17923,7 +17927,7 @@
         <v>邵卿城·退场·屋前西侧·500分</v>
       </c>
       <c r="F8" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="G8" t="s">
         <v>1627</v>
@@ -17964,7 +17968,7 @@
         <v>李霖·退场·唱晚池鱼塘·300分</v>
       </c>
       <c r="F9" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="G9" t="s">
         <v>1626</v>
@@ -18005,7 +18009,7 @@
         <v>韩非子·退场·祈星台北·300分</v>
       </c>
       <c r="F10" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="G10" t="s">
         <v>1626</v>
@@ -18046,7 +18050,7 @@
         <v>苏不尘·退场·帮会药师·300分</v>
       </c>
       <c r="F11" t="s">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="G11" t="s">
         <v>1626</v>
@@ -18087,7 +18091,7 @@
         <v>高九问·退场·帮会天工·500分</v>
       </c>
       <c r="F12" t="s">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="G12" t="s">
         <v>1627</v>
@@ -18128,7 +18132,7 @@
         <v>鲁印·退场·会友台东侧·300分</v>
       </c>
       <c r="F13" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="G13" t="s">
         <v>1626</v>
@@ -18159,7 +18163,7 @@
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.15">
       <c r="C14" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="D14" t="s">
         <v>1613</v>
@@ -18169,7 +18173,7 @@
         <v>雄爷·退场·帮会书柜旁·200分</v>
       </c>
       <c r="F14" t="s">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="G14" t="s">
         <v>1625</v>
@@ -18210,7 +18214,7 @@
         <v>凯风·退场·帮会内宴席·100分</v>
       </c>
       <c r="F15" t="s">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="G15" t="s">
         <v>1623</v>
@@ -18251,7 +18255,7 @@
         <v>贾扁·退场·屋檐顶西北·100分</v>
       </c>
       <c r="F16" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="G16" t="s">
         <v>1623</v>
@@ -18292,7 +18296,7 @@
         <v>梦香菲·退场·大旗东侧·100分</v>
       </c>
       <c r="F17" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="G17" t="s">
         <v>1623</v>
@@ -18333,7 +18337,7 @@
         <v>凤妞·退场·大旗西侧方·100分</v>
       </c>
       <c r="F18" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="G18" t="s">
         <v>1623</v>
@@ -18374,7 +18378,7 @@
         <v>韩荞生·退场·流星赶月·100分</v>
       </c>
       <c r="F19" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="G19" t="s">
         <v>1623</v>
@@ -18415,7 +18419,7 @@
         <v>黄剑翔·退场·流星赶月·100分</v>
       </c>
       <c r="F20" t="s">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="G20" t="s">
         <v>1623</v>
@@ -18456,7 +18460,7 @@
         <v>三石叔·退场·落日牧场·100分</v>
       </c>
       <c r="F21" t="s">
-        <v>1656</v>
+        <v>1655</v>
       </c>
       <c r="G21" t="s">
         <v>1623</v>
@@ -18497,7 +18501,7 @@
         <v>陈士美·退场·山水田园·200分</v>
       </c>
       <c r="F22" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="G22" t="s">
         <v>1625</v>
@@ -18546,14 +18550,14 @@
         <v>1636</v>
       </c>
       <c r="E24" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="Q24" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="本次宣战进攻将在30秒后正式开始。",szTarget="%",szNote="帮会宣战·领地·30秒",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·开启剩余",nTime="30,帮会宣战·领地·开启剩余;35,帮会宣战·领地·正式开启",key="帮会宣战",nRefresh=0,},},},</v>
       </c>
       <c r="R24" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.15">
@@ -18564,14 +18568,14 @@
         <v>1637</v>
       </c>
       <c r="E25" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="Q25" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="本次宣战进攻将在10秒后正式开始。",szTarget="%",szNote="帮会宣战·领地·10秒",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·开启剩余",nTime="10,帮会宣战·领地·开启剩余;15,帮会宣战·领地·正式开启",key="帮会宣战",nRefresh=0,},},},</v>
       </c>
       <c r="R25" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.15">
@@ -18586,22 +18590,22 @@
       </c>
       <c r="Q26" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="当前已开战，请直接对话进入被宣战方帮会领地。",szNote="帮会宣战·领地·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=0,nFrame=4,szName="帮会宣战·领地·正式开启",nTime=5,key="帮会宣战",},},},</v>
+        <v>{szContent="当前已开战，请直接对话进入被宣战方帮会领地。",szNote="帮会宣战·领地·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·正式开启",nTime=5,key="帮会宣战",},},},</v>
       </c>
       <c r="R26" t="s">
-        <v>1640</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A27" t="s">
+        <v>1674</v>
+      </c>
       <c r="B27">
-        <v>153</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1673</v>
+        <v>-21</v>
       </c>
       <c r="Q27" t="str">
         <f t="shared" si="0"/>
-        <v>},[153]={</v>
+        <v>},[-21]={</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.15">
@@ -18609,21 +18613,105 @@
         <v>1635</v>
       </c>
       <c r="D28" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="E28" t="s">
         <v>1641</v>
       </c>
       <c r="Q28" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="本次宣战进攻将在10秒后正式开始。",szTarget="%",szNote="帮会宣战·领地·10秒",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·开启剩余",nTime="10,帮会宣战·领地·开启剩余;15,帮会宣战·领地·正式开启",key="帮会宣战",nRefresh=0,},},},</v>
+        <v>{szContent="本次宣战进攻将在30秒后正式开始。",szTarget="%",szNote="帮会宣战·领地·30秒",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·开启剩余",nTime="30,帮会宣战·领地·开启剩余;35,帮会宣战·领地·正式开启",key="帮会宣战",nRefresh=0,},},},</v>
       </c>
       <c r="R28" t="s">
         <v>1671</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="C29" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1637</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1640</v>
+      </c>
       <c r="Q29" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="本次宣战进攻将在10秒后正式开始。",szTarget="%",szNote="帮会宣战·领地·10秒",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·开启剩余",nTime="10,帮会宣战·领地·开启剩余;15,帮会宣战·领地·正式开启",key="帮会宣战",nRefresh=0,},},},</v>
+      </c>
+      <c r="R29" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="D30" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1639</v>
+      </c>
+      <c r="N30">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="当前已开战，请直接对话进入被宣战方帮会领地。",szNote="帮会宣战·领地·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·正式开启",nTime=5,key="帮会宣战",},},},</v>
+      </c>
+      <c r="R30" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A31" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B31">
+        <v>153</v>
+      </c>
+      <c r="Q31" t="str">
+        <f t="shared" si="0"/>
+        <v>},[153]={</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="C32" t="s">
+        <v>1635</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1637</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1640</v>
+      </c>
+      <c r="Q32" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="本次宣战进攻将在10秒后正式开始。",szTarget="%",szNote="帮会宣战·领地·10秒",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·开启剩余",nTime="10,帮会宣战·领地·开启剩余;15,帮会宣战·领地·正式开启",key="帮会宣战",nRefresh=0,},},},</v>
+      </c>
+      <c r="R32" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="33" spans="4:18" x14ac:dyDescent="0.15">
+      <c r="D33" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1639</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="Q33" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="当前已开战，请直接对话进入被宣战方帮会领地。",szNote="帮会宣战·领地·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·正式开启",nTime=5,key="帮会宣战",},},},</v>
+      </c>
+      <c r="R33" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="34" spans="4:18" x14ac:dyDescent="0.15">
+      <c r="Q34" t="str">
         <f t="shared" si="0"/>
         <v>},},}</v>
       </c>
@@ -18714,10 +18802,10 @@
         <v>1616</v>
       </c>
       <c r="P3" s="37" t="s">
+        <v>1646</v>
+      </c>
+      <c r="Q3" s="37" t="s">
         <v>1647</v>
-      </c>
-      <c r="Q3" s="37" t="s">
-        <v>1648</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.15">
@@ -18768,10 +18856,10 @@
         <v>1631</v>
       </c>
       <c r="P7" s="37" t="s">
+        <v>1646</v>
+      </c>
+      <c r="Q7" s="37" t="s">
         <v>1647</v>
-      </c>
-      <c r="Q7" s="37" t="s">
-        <v>1648</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.15">

--- a/阵营/帮会领地战.xlsx
+++ b/阵营/帮会领地战.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -5042,7 +5042,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5168,13 +5168,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -5674,7 +5667,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5683,10 +5676,10 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5698,7 +5691,7 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5710,7 +5703,7 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5722,7 +5715,7 @@
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5734,7 +5727,7 @@
     <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -5746,7 +5739,7 @@
     <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -6256,7 +6249,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1786118889000,</v>
+        <v>nTimeStamp = 1786286205000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -17402,7 +17395,7 @@
         <v>1604</v>
       </c>
       <c r="E3" t="str">
-        <f>C3&amp;"·退场·"&amp;F3&amp;G3</f>
+        <f t="shared" ref="E3:E18" si="0">C3&amp;"·退场·"&amp;F3&amp;G3</f>
         <v>陈士美·退场·山水田园·200分</v>
       </c>
       <c r="F3" t="s">
@@ -17423,15 +17416,12 @@
       <c r="N3">
         <v>1</v>
       </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
       <c r="Q3" t="str">
-        <f t="shared" ref="Q3:Q34" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(I3),ISBLANK(J3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(I2)=FALSE,ISBLANK(J2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(H3&lt;&gt;"","col={"&amp;H3&amp;"},","")&amp;IF(I3&gt;0,"bSearch=true,","")&amp;IF(J3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(K3&gt;0,"szVoice="""&amp;K3&amp;""",","")&amp;IF(L3&gt;0,"bTeamChannel=true,","")&amp;IF(M3&gt;0,"bWhisperChannel=true,","")&amp;IF(N3&gt;0,"bCenterAlarm=true,","")&amp;IF(O3&gt;0,"bScreenHead=true,","")&amp;IF(P3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(R3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,R3:AAC3)&amp;"},","")&amp;"},")))</f>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="陈士美",szNote="陈士美·退场·山水田园·200分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="陈士美·退场·山水田园·200分",nTime=30,key="陈士美·退场",nRefresh=1,},},},</v>
+        <f t="shared" ref="Q3:Q34" si="1">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(D3),ISBLANK(I3),ISBLANK(J3),OR(ISBLANK(B2)=FALSE,ISBLANK(D2)=FALSE,ISBLANK(I2)=FALSE,ISBLANK(J2)=FALSE)),"},},}",IF(ISBLANK(D3),"","{szContent="""&amp;D3&amp;""","&amp;IF(C3&lt;&gt;"","szTarget="""&amp;C3&amp;""",","")&amp;IF(E3&lt;&gt;"","szNote="""&amp;E3&amp;""",","")&amp;IF(H3&lt;&gt;"","col={"&amp;H3&amp;"},","")&amp;IF(I3&gt;0,"bSearch=true,","")&amp;IF(J3&gt;0,"bReg=true,","")&amp;"[14]={"&amp;IF(K3&gt;0,"szVoice="""&amp;K3&amp;""",","")&amp;IF(L3&gt;0,"bTeamChannel=true,","")&amp;IF(M3&gt;0,"bWhisperChannel=true,","")&amp;IF(N3&gt;0,"bCenterAlarm=true,","")&amp;IF(O3&gt;0,"bScreenHead=true,","")&amp;IF(P3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(R3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,R3:AAC3)&amp;"},","")&amp;"},")))</f>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="陈士美",szNote="陈士美·退场·山水田园·200分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="陈士美·退场·山水田园·200分",nTime=30,key="陈士美·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R3" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E3&amp;""",nTime=30,key="""&amp;C3&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" ref="R3:R18" si="2">"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E3&amp;""",nTime=30,key="""&amp;C3&amp;"·退场"""&amp;",nRefresh=1,},"</f>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="陈士美·退场·山水田园·200分",nTime=30,key="陈士美·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17443,7 +17433,7 @@
         <v>1604</v>
       </c>
       <c r="E4" t="str">
-        <f>C4&amp;"·退场·"&amp;F4&amp;G4</f>
+        <f t="shared" si="0"/>
         <v>三石叔·退场·落日牧场·100分</v>
       </c>
       <c r="F4" t="s">
@@ -17464,15 +17454,12 @@
       <c r="N4">
         <v>1</v>
       </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
       <c r="Q4" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="三石叔",szNote="三石叔·退场·落日牧场·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="三石叔·退场·落日牧场·100分",nTime=30,key="三石叔·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="三石叔",szNote="三石叔·退场·落日牧场·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="三石叔·退场·落日牧场·100分",nTime=30,key="三石叔·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R4" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E4&amp;""",nTime=30,key="""&amp;C4&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="三石叔·退场·落日牧场·100分",nTime=30,key="三石叔·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17484,7 +17471,7 @@
         <v>1604</v>
       </c>
       <c r="E5" t="str">
-        <f>C5&amp;"·退场·"&amp;F5&amp;G5</f>
+        <f t="shared" si="0"/>
         <v>黄剑翔·退场·流星赶月·100分</v>
       </c>
       <c r="F5" t="s">
@@ -17505,15 +17492,12 @@
       <c r="N5">
         <v>1</v>
       </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
       <c r="Q5" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="黄剑翔",szNote="黄剑翔·退场·流星赶月·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="黄剑翔·退场·流星赶月·100分",nTime=30,key="黄剑翔·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="黄剑翔",szNote="黄剑翔·退场·流星赶月·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="黄剑翔·退场·流星赶月·100分",nTime=30,key="黄剑翔·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R5" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E5&amp;""",nTime=30,key="""&amp;C5&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="黄剑翔·退场·流星赶月·100分",nTime=30,key="黄剑翔·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17525,7 +17509,7 @@
         <v>1604</v>
       </c>
       <c r="E6" t="str">
-        <f>C6&amp;"·退场·"&amp;F6&amp;G6</f>
+        <f t="shared" si="0"/>
         <v>韩荞生·退场·流星赶月·100分</v>
       </c>
       <c r="F6" t="s">
@@ -17546,15 +17530,12 @@
       <c r="N6">
         <v>1</v>
       </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
       <c r="Q6" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="韩荞生",szNote="韩荞生·退场·流星赶月·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="韩荞生·退场·流星赶月·100分",nTime=30,key="韩荞生·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="韩荞生",szNote="韩荞生·退场·流星赶月·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="韩荞生·退场·流星赶月·100分",nTime=30,key="韩荞生·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R6" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E6&amp;""",nTime=30,key="""&amp;C6&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="韩荞生·退场·流星赶月·100分",nTime=30,key="韩荞生·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17566,7 +17547,7 @@
         <v>1604</v>
       </c>
       <c r="E7" t="str">
-        <f>C7&amp;"·退场·"&amp;F7&amp;G7</f>
+        <f t="shared" si="0"/>
         <v>凤妞·退场·大旗西侧方·100分</v>
       </c>
       <c r="F7" t="s">
@@ -17587,15 +17568,12 @@
       <c r="N7">
         <v>1</v>
       </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
       <c r="Q7" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="凤妞",szNote="凤妞·退场·大旗西侧方·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="凤妞·退场·大旗西侧方·100分",nTime=30,key="凤妞·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="凤妞",szNote="凤妞·退场·大旗西侧方·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="凤妞·退场·大旗西侧方·100分",nTime=30,key="凤妞·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R7" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E7&amp;""",nTime=30,key="""&amp;C7&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="凤妞·退场·大旗西侧方·100分",nTime=30,key="凤妞·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17607,7 +17585,7 @@
         <v>1604</v>
       </c>
       <c r="E8" t="str">
-        <f>C8&amp;"·退场·"&amp;F8&amp;G8</f>
+        <f t="shared" si="0"/>
         <v>梦香菲·退场·大旗东侧·100分</v>
       </c>
       <c r="F8" t="s">
@@ -17628,15 +17606,12 @@
       <c r="N8">
         <v>1</v>
       </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
       <c r="Q8" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="梦香菲",szNote="梦香菲·退场·大旗东侧·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="梦香菲·退场·大旗东侧·100分",nTime=30,key="梦香菲·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="梦香菲",szNote="梦香菲·退场·大旗东侧·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="梦香菲·退场·大旗东侧·100分",nTime=30,key="梦香菲·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R8" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E8&amp;""",nTime=30,key="""&amp;C8&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="梦香菲·退场·大旗东侧·100分",nTime=30,key="梦香菲·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17648,7 +17623,7 @@
         <v>1604</v>
       </c>
       <c r="E9" t="str">
-        <f>C9&amp;"·退场·"&amp;F9&amp;G9</f>
+        <f t="shared" si="0"/>
         <v>贾扁·退场·屋檐顶西北·100分</v>
       </c>
       <c r="F9" t="s">
@@ -17669,15 +17644,12 @@
       <c r="N9">
         <v>1</v>
       </c>
-      <c r="P9">
-        <v>1</v>
-      </c>
       <c r="Q9" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="贾扁",szNote="贾扁·退场·屋檐顶西北·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="贾扁·退场·屋檐顶西北·100分",nTime=30,key="贾扁·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="贾扁",szNote="贾扁·退场·屋檐顶西北·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="贾扁·退场·屋檐顶西北·100分",nTime=30,key="贾扁·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R9" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E9&amp;""",nTime=30,key="""&amp;C9&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="贾扁·退场·屋檐顶西北·100分",nTime=30,key="贾扁·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17689,7 +17661,7 @@
         <v>1604</v>
       </c>
       <c r="E10" t="str">
-        <f>C10&amp;"·退场·"&amp;F10&amp;G10</f>
+        <f t="shared" si="0"/>
         <v>凯风·退场·帮会内宴席·100分</v>
       </c>
       <c r="F10" t="s">
@@ -17710,15 +17682,12 @@
       <c r="N10">
         <v>1</v>
       </c>
-      <c r="P10">
-        <v>1</v>
-      </c>
       <c r="Q10" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="凯风",szNote="凯风·退场·帮会内宴席·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="凯风·退场·帮会内宴席·100分",nTime=30,key="凯风·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="凯风",szNote="凯风·退场·帮会内宴席·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="凯风·退场·帮会内宴席·100分",nTime=30,key="凯风·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R10" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E10&amp;""",nTime=30,key="""&amp;C10&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="凯风·退场·帮会内宴席·100分",nTime=30,key="凯风·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17730,7 +17699,7 @@
         <v>1604</v>
       </c>
       <c r="E11" t="str">
-        <f>C11&amp;"·退场·"&amp;F11&amp;G11</f>
+        <f t="shared" si="0"/>
         <v>雄爷·退场·帮会书柜旁·200分</v>
       </c>
       <c r="F11" t="s">
@@ -17751,15 +17720,12 @@
       <c r="N11">
         <v>1</v>
       </c>
-      <c r="P11">
-        <v>1</v>
-      </c>
       <c r="Q11" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="雄爷",szNote="雄爷·退场·帮会书柜旁·200分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="雄爷·退场·帮会书柜旁·200分",nTime=30,key="雄爷·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="雄爷",szNote="雄爷·退场·帮会书柜旁·200分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="雄爷·退场·帮会书柜旁·200分",nTime=30,key="雄爷·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R11" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E11&amp;""",nTime=30,key="""&amp;C11&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="雄爷·退场·帮会书柜旁·200分",nTime=30,key="雄爷·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17771,7 +17737,7 @@
         <v>1604</v>
       </c>
       <c r="E12" t="str">
-        <f>C12&amp;"·退场·"&amp;F12&amp;G12</f>
+        <f t="shared" si="0"/>
         <v>鲁印·退场·会友台东侧·300分</v>
       </c>
       <c r="F12" t="s">
@@ -17792,15 +17758,12 @@
       <c r="N12">
         <v>1</v>
       </c>
-      <c r="P12">
-        <v>1</v>
-      </c>
       <c r="Q12" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="鲁印",szNote="鲁印·退场·会友台东侧·300分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="鲁印·退场·会友台东侧·300分",nTime=30,key="鲁印·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="鲁印",szNote="鲁印·退场·会友台东侧·300分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="鲁印·退场·会友台东侧·300分",nTime=30,key="鲁印·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R12" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E12&amp;""",nTime=30,key="""&amp;C12&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="鲁印·退场·会友台东侧·300分",nTime=30,key="鲁印·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17812,7 +17775,7 @@
         <v>1604</v>
       </c>
       <c r="E13" t="str">
-        <f>C13&amp;"·退场·"&amp;F13&amp;G13</f>
+        <f t="shared" si="0"/>
         <v>高九问·退场·帮会天工·500分</v>
       </c>
       <c r="F13" t="s">
@@ -17833,15 +17796,12 @@
       <c r="N13">
         <v>1</v>
       </c>
-      <c r="P13">
-        <v>1</v>
-      </c>
       <c r="Q13" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="高九问",szNote="高九问·退场·帮会天工·500分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="高九问·退场·帮会天工·500分",nTime=30,key="高九问·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="高九问",szNote="高九问·退场·帮会天工·500分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="高九问·退场·帮会天工·500分",nTime=30,key="高九问·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R13" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E13&amp;""",nTime=30,key="""&amp;C13&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="高九问·退场·帮会天工·500分",nTime=30,key="高九问·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17853,7 +17813,7 @@
         <v>1604</v>
       </c>
       <c r="E14" t="str">
-        <f>C14&amp;"·退场·"&amp;F14&amp;G14</f>
+        <f t="shared" si="0"/>
         <v>苏不尘·退场·帮会药师·300分</v>
       </c>
       <c r="F14" t="s">
@@ -17874,15 +17834,12 @@
       <c r="N14">
         <v>1</v>
       </c>
-      <c r="P14">
-        <v>1</v>
-      </c>
       <c r="Q14" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="苏不尘",szNote="苏不尘·退场·帮会药师·300分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="苏不尘·退场·帮会药师·300分",nTime=30,key="苏不尘·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="苏不尘",szNote="苏不尘·退场·帮会药师·300分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="苏不尘·退场·帮会药师·300分",nTime=30,key="苏不尘·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R14" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E14&amp;""",nTime=30,key="""&amp;C14&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="苏不尘·退场·帮会药师·300分",nTime=30,key="苏不尘·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17894,7 +17851,7 @@
         <v>1604</v>
       </c>
       <c r="E15" t="str">
-        <f>C15&amp;"·退场·"&amp;F15&amp;G15</f>
+        <f t="shared" si="0"/>
         <v>韩非子·退场·祈星台北·300分</v>
       </c>
       <c r="F15" t="s">
@@ -17915,15 +17872,12 @@
       <c r="N15">
         <v>1</v>
       </c>
-      <c r="P15">
-        <v>1</v>
-      </c>
       <c r="Q15" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="韩非子",szNote="韩非子·退场·祈星台北·300分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="韩非子·退场·祈星台北·300分",nTime=30,key="韩非子·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="韩非子",szNote="韩非子·退场·祈星台北·300分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="韩非子·退场·祈星台北·300分",nTime=30,key="韩非子·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R15" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E15&amp;""",nTime=30,key="""&amp;C15&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="韩非子·退场·祈星台北·300分",nTime=30,key="韩非子·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17935,7 +17889,7 @@
         <v>1604</v>
       </c>
       <c r="E16" t="str">
-        <f>C16&amp;"·退场·"&amp;F16&amp;G16</f>
+        <f t="shared" si="0"/>
         <v>李霖·退场·唱晚池鱼塘·300分</v>
       </c>
       <c r="F16" t="s">
@@ -17956,15 +17910,12 @@
       <c r="N16">
         <v>1</v>
       </c>
-      <c r="P16">
-        <v>1</v>
-      </c>
       <c r="Q16" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="李霖",szNote="李霖·退场·唱晚池鱼塘·300分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="李霖·退场·唱晚池鱼塘·300分",nTime=30,key="李霖·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="李霖",szNote="李霖·退场·唱晚池鱼塘·300分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="李霖·退场·唱晚池鱼塘·300分",nTime=30,key="李霖·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R16" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E16&amp;""",nTime=30,key="""&amp;C16&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="李霖·退场·唱晚池鱼塘·300分",nTime=30,key="李霖·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -17976,7 +17927,7 @@
         <v>1604</v>
       </c>
       <c r="E17" t="str">
-        <f>C17&amp;"·退场·"&amp;F17&amp;G17</f>
+        <f t="shared" si="0"/>
         <v>邵卿城·退场·屋前西侧·500分</v>
       </c>
       <c r="F17" t="s">
@@ -17997,15 +17948,12 @@
       <c r="N17">
         <v>1</v>
       </c>
-      <c r="P17">
-        <v>1</v>
-      </c>
       <c r="Q17" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="邵卿城",szNote="邵卿城·退场·屋前西侧·500分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="邵卿城·退场·屋前西侧·500分",nTime=30,key="邵卿城·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="邵卿城",szNote="邵卿城·退场·屋前西侧·500分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="邵卿城·退场·屋前西侧·500分",nTime=30,key="邵卿城·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R17" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E17&amp;""",nTime=30,key="""&amp;C17&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="邵卿城·退场·屋前西侧·500分",nTime=30,key="邵卿城·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -18017,7 +17965,7 @@
         <v>1604</v>
       </c>
       <c r="E18" t="str">
-        <f>C18&amp;"·退场·"&amp;F18&amp;G18</f>
+        <f t="shared" si="0"/>
         <v>甄琦·退场·屋门前东侧·100分</v>
       </c>
       <c r="F18" t="s">
@@ -18038,15 +17986,12 @@
       <c r="N18">
         <v>1</v>
       </c>
-      <c r="P18">
-        <v>1</v>
-      </c>
       <c r="Q18" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="甄琦",szNote="甄琦·退场·屋门前东侧·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="甄琦·退场·屋门前东侧·100分",nTime=30,key="甄琦·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="甄琦",szNote="甄琦·退场·屋门前东侧·100分",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="甄琦·退场·屋门前东侧·100分",nTime=30,key="甄琦·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R18" t="str">
-        <f>"{nClass=14,nIcon=13,nFrame=1,szName="""&amp;E18&amp;""",nTime=30,key="""&amp;C18&amp;"·退场"""&amp;",nRefresh=1,},"</f>
+        <f t="shared" si="2"/>
         <v>{nClass=14,nIcon=13,nFrame=1,szName="甄琦·退场·屋门前东侧·100分",nTime=30,key="甄琦·退场",nRefresh=1,},</v>
       </c>
     </row>
@@ -18072,12 +18017,9 @@
       <c r="N19">
         <v>1</v>
       </c>
-      <c r="P19">
-        <v>1</v>
-      </c>
       <c r="Q19" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="%",szNote="{$sender}·退场",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="{$sender}·退场",nTime=30,key="{$sender}·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="帮会的兄弟们，我且先修整下！",szTarget="%",szNote="{$sender}·退场",col={255,255,255,},bSearch=true,[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=1,szName="{$sender}·退场",nTime=30,key="{$sender}·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R19" t="s">
         <v>1626</v>
@@ -18102,12 +18044,9 @@
       <c r="N20">
         <v>1</v>
       </c>
-      <c r="P20">
-        <v>1</v>
-      </c>
       <c r="Q20" t="str">
-        <f t="shared" si="0"/>
-        <v>{szContent="[帮会宣战][帮会大旗]已被敌方攻破！诸位兄弟！团结一致！",szTarget="%",szNote="帮会大旗·退场·800分",col={255,255,255,},[14]={bTeamChannel=true,bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=14,nIcon=591,nFrame=1,szName="帮会大旗·损毁·800分",nTime=30,key="帮会大旗·退场",nRefresh=1,},},},</v>
+        <f t="shared" si="1"/>
+        <v>{szContent="[帮会宣战][帮会大旗]已被敌方攻破！诸位兄弟！团结一致！",szTarget="%",szNote="帮会大旗·退场·800分",col={255,255,255,},[14]={bTeamChannel=true,bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=591,nFrame=1,szName="帮会大旗·损毁·800分",nTime=30,key="帮会大旗·退场",nRefresh=1,},},},</v>
       </c>
       <c r="R20" t="s">
         <v>1629</v>
@@ -18124,7 +18063,7 @@
         <v>1</v>
       </c>
       <c r="Q21" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="恭喜侠士帮会宣战·领地获胜！已为您添加增益状态。",szNote="帮会宣战·领地·获胜",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=0,szName="帮会宣战·领地·获胜",nTime=30,key="帮会宣战",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="R21" t="s">
@@ -18142,7 +18081,7 @@
         <v>1635</v>
       </c>
       <c r="Q22" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="最近七天内，帮会宣战·领地失利，已为侠士添加不利状态。",szNote="帮会宣战·领地·失败",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=8,szName="帮会宣战·领地·失败",nTime=30,key="帮会宣战",},{nClass=14,nIcon=13,szName="诛恶事件",nTime=-2,key="诛恶事件",},{nClass=14,nIcon=13,szName="通用事件",nTime=-2,key="通用事件",},{nClass=14,nIcon=13,nTime=-2,szName="金水镇",key="金水镇",},{nClass=14,nIcon=13,nTime=-2,szName="巴陵县",key="巴陵县",},{nClass=14,nIcon=13,nTime=-2,szName="龙门荒漠",key="龙门荒漠",},{nClass=14,nIcon=13,nTime=-2,szName="南屏山",key="南屏山",},{nClass=14,nIcon=13,nTime=-2,szName="昆仑",key="昆仑",},{nClass=14,nIcon=13,nTime=-2,szName="白龙口",key="白龙口",},{nClass=14,nIcon=13,nTime=-2,szName="无量山",key="无量山",},{nClass=14,nIcon=13,nTime=-2,szName="黑龙沼",key="黑龙沼",},{nClass=14,nIcon=13,nTime=-2,szName="阴山大草原",key="阴山大草原",},{nClass=14,nIcon=13,nTime=-2,szName="黑戈壁",key="黑戈壁",},{nClass=14,nIcon=13,nTime=-2,szName="鲲鹏岛",key="鲲鹏岛",},},},</v>
       </c>
       <c r="R22" t="s">
@@ -18160,7 +18099,7 @@
         <v>-2</v>
       </c>
       <c r="Q23" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>},[-2]={</v>
       </c>
     </row>
@@ -18175,7 +18114,7 @@
         <v>1</v>
       </c>
       <c r="Q24" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="当前已开战，请直接对话进入被宣战方帮会领地。",szNote="帮会宣战·领地·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·正式开启",nTime=5,key="帮会宣战",},},},</v>
       </c>
       <c r="R24" t="s">
@@ -18193,7 +18132,7 @@
         <v>1642</v>
       </c>
       <c r="Q25" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本次宣战进攻将在10秒后正式开始。",szTarget="%",szNote="帮会宣战·领地·10秒",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·开启剩余",nTime="10,帮会宣战·领地·开启剩余;15,帮会宣战·领地·正式开启",key="帮会宣战",nRefresh=0,},},},</v>
       </c>
       <c r="R25" t="s">
@@ -18211,7 +18150,7 @@
         <v>1645</v>
       </c>
       <c r="Q26" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本次宣战进攻将在30秒后正式开始。",szTarget="%",szNote="帮会宣战·领地·30秒",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·开启剩余",nTime="30,帮会宣战·领地·开启剩余;35,帮会宣战·领地·正式开启",key="帮会宣战",nRefresh=0,},},},</v>
       </c>
       <c r="R26" t="s">
@@ -18226,7 +18165,7 @@
         <v>-21</v>
       </c>
       <c r="Q27" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>},[-21]={</v>
       </c>
     </row>
@@ -18241,7 +18180,7 @@
         <v>1</v>
       </c>
       <c r="Q28" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="当前已开战，请直接对话进入被宣战方帮会领地。",szNote="帮会宣战·领地·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·正式开启",nTime=5,key="帮会宣战",},},},</v>
       </c>
       <c r="R28" t="s">
@@ -18259,7 +18198,7 @@
         <v>1642</v>
       </c>
       <c r="Q29" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本次宣战进攻将在10秒后正式开始。",szTarget="%",szNote="帮会宣战·领地·10秒",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·开启剩余",nTime="10,帮会宣战·领地·开启剩余;15,帮会宣战·领地·正式开启",key="帮会宣战",nRefresh=0,},},},</v>
       </c>
       <c r="R29" t="s">
@@ -18277,7 +18216,7 @@
         <v>1645</v>
       </c>
       <c r="Q30" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本次宣战进攻将在30秒后正式开始。",szTarget="%",szNote="帮会宣战·领地·30秒",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·开启剩余",nTime="30,帮会宣战·领地·开启剩余;35,帮会宣战·领地·正式开启",key="帮会宣战",nRefresh=0,},},},</v>
       </c>
       <c r="R30" t="s">
@@ -18292,7 +18231,7 @@
         <v>153</v>
       </c>
       <c r="Q31" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>},[153]={</v>
       </c>
     </row>
@@ -18307,7 +18246,7 @@
         <v>1</v>
       </c>
       <c r="Q32" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="当前已开战，请直接对话进入被宣战方帮会领地。",szNote="帮会宣战·领地·正式开始",[14]={bCenterAlarm=true,},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·正式开启",nTime=5,key="帮会宣战",},},},</v>
       </c>
       <c r="R32" t="s">
@@ -18325,7 +18264,7 @@
         <v>1642</v>
       </c>
       <c r="Q33" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>{szContent="本次宣战进攻将在10秒后正式开始。",szTarget="%",szNote="帮会宣战·领地·10秒",[14]={},tCountdown={{nClass=14,nIcon=13,nFrame=4,szName="帮会宣战·领地·开启剩余",nTime="10,帮会宣战·领地·开启剩余;15,帮会宣战·领地·正式开启",key="帮会宣战",nRefresh=0,},},},</v>
       </c>
       <c r="R33" t="s">
@@ -18334,7 +18273,7 @@
     </row>
     <row r="34" spans="3:18">
       <c r="Q34" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>},},}</v>
       </c>
     </row>
@@ -18418,7 +18357,7 @@
         <v>1649</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N8" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="N3:N9" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="帮会宣战·领地正式开始！\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,szName="宣战·正式开始",nTime=5,key="帮会宣战",},{nClass=20,nIcon=13,szName="诛恶事件",nTime=-1,nRefresh=2700,key="诛恶事件",},{nClass=20,nIcon=13,szName="通用事件",nTime=-1,nRefresh=2700,key="通用事件",},{nClass=20,nIcon=13,nTime=-1,szName="金水镇",nRefresh=2700,key="金水镇",},{nClass=20,nIcon=13,nTime=-1,szName="巴陵县",nRefresh=2700,key="巴陵县",},{nClass=20,nIcon=13,nTime=-1,szName="龙门荒漠",nRefresh=2700,key="龙门荒漠",},{nClass=20,nIcon=13,nTime=-1,szName="南屏山",nRefresh=2700,key="南屏山",},{nClass=20,nIcon=13,nTime=-1,szName="昆仑",nRefresh=2700,key="昆仑",},{nClass=20,nIcon=13,nTime=-1,szName="白龙口",nRefresh=2700,key="白龙口",},{nClass=20,nIcon=13,nTime=-1,szName="无量山",nRefresh=2700,key="无量山",},{nClass=20,nIcon=13,nTime=-1,szName="黑龙沼",nRefresh=2700,key="黑龙沼",},{nClass=20,nIcon=13,nTime=-1,szName="阴山大草原",nRefresh=2700,key="阴山大草原",},{nClass=20,nIcon=13,nTime=-1,szName="黑戈壁",nRefresh=2700,key="黑戈壁",},{nClass=20,nIcon=13,nTime=-1,szName="鲲鹏岛",nRefresh=2700,key="鲲鹏岛",},},},</v>
       </c>
       <c r="O3" t="s">
@@ -18496,7 +18435,7 @@
     </row>
     <row r="9" spans="1:17">
       <c r="N9" t="str">
-        <f>IF(ISBLANK(B9)=FALSE,IF(ISBLANK(B8),"},["&amp;B9&amp;"]={","["&amp;B9&amp;"]={"),IF(AND(ISBLANK(B9),ISBLANK(C9),ISBLANK(F9),ISBLANK(G9),OR(ISBLANK(B8)=FALSE,ISBLANK(C8)=FALSE,ISBLANK(F8)=FALSE,ISBLANK(G8)=FALSE)),"},},}",IF(ISBLANK(C9),"","{szContent="""&amp;C9&amp;""","&amp;IF(D9&lt;&gt;"","szNote="""&amp;D9&amp;""",","")&amp;IF(E9&lt;&gt;"","col={"&amp;E9&amp;"},","")&amp;IF(F9&gt;0,"bSearch=true,","")&amp;IF(G9&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H9&gt;0,"szVoice="""&amp;H9&amp;""",","")&amp;IF(I9&gt;0,"bTeamChannel=true,","")&amp;IF(J9&gt;0,"bWhisperChannel=true,","")&amp;IF(K9&gt;0,"bCenterAlarm=true,","")&amp;IF(L9&gt;0,"bScreenHead=true,","")&amp;IF(M9&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O9&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O9:AAA9)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
